--- a/projects/auto_page/autopageMKII/assets/tables/Accel_mode_test.xlsx
+++ b/projects/auto_page/autopageMKII/assets/tables/Accel_mode_test.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Failed_Orders" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Processed_Logs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -5769,30 +5770,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>260724G8418ERN</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>please input serial.
 ⚠️ ไม่สามารถระบุ item ที่ขาด SN ได้ (ตรวจสอบ used_serials manually) (ด่านที่ติด: ออกบิลเรียบร้อย)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>2026-07-24 11:59:51</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>260724G7YH78BY</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Message: no such element: Unable to locate element: {"method":"xpath","selector":"/html/body/div[2]/div[2]/div/div[2]/div/div[2]/div[1]/div[2]/div/div/div[2]/div/div/span/span[1]/span/ul/li/input"}
   (Session info: chrome=150.0.7871.182); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
@@ -5819,9 +5820,70 @@
  (ด่านที่ติด: ใส่ชื่อลูกค้าสำเร็จ)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>2026-07-24 12:00:03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tracking</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>bill_no</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sn</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>error_category</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>remark</t>
         </is>
       </c>
     </row>
